--- a/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-09_Customer_Servicing_Facility_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-09_Customer_Servicing_Facility_v1.0.xlsx
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -16795,12 +16795,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>One user per role - agent1 and agent2 (CSF_AGENT), sup1 (CSF_SUPERVISOR), mgmt1 (CSF_MANAGEMENT), the System Administrator, ao (MKT_AO, no CSF role). The build design plans the demo users csfagent, csfagent2, csfsup and csfmgmt for the same roles.</t>
+          <t>One user per role - agent1 and agent2 (CSF_AGENT), sup1 (CSF_SUPERVISOR), mgmt1 (CSF_MANAGEMENT), the System Administrator, ao (MKT_AO, no CSF role). The build design plans the SIT/UAT users csfagent, csfagent2, csfsup and csfmgmt for the same roles.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Created by the test lead through User Access requests on SIT; planned demo seed V1940 of the build design</t>
+          <t>Created by the test lead through User Access requests on SIT; planned seed V1940 of the build design</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -16825,7 +16825,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Prepared by the test lead on SIT from masked demo clients (V981) and accounts keyed in the BRD-1 screens</t>
+          <t>Prepared by the test lead on SIT from masked seed clients (V981) and accounts keyed in the BRD-1 screens</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
